--- a/XB6A/4. K98 Base - XB6A.xlsx
+++ b/XB6A/4. K98 Base - XB6A.xlsx
@@ -49,7 +49,7 @@
     <t xml:space="preserve">PHỤ LỤC KIỂM TRA CAO ĐỘ, KÍCH THƯỚC HÌNH HỌC</t>
   </si>
   <si>
-    <t xml:space="preserve">Kèm theo BBNT số: 17.NĐXB6A/CVXD ngày 03 tháng 09 năm 2026</t>
+    <t xml:space="preserve">Kèm theo BBNT số: 17.NĐXB6A/CVXD ngày 06 tháng 09 năm 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Dự án: Xây dựng HTKT Khu tái định cư phục vụ di dân xã Hải Hà, thị xã Nghi Sơn, tỉnh Thanh Hóa.</t>
@@ -178,19 +178,19 @@
     <t xml:space="preserve">                 </t>
   </si>
   <si>
-    <t xml:space="preserve">Kèm theo BBNT số: 19.NĐXB6A/CVXD ngày 04 tháng 09 năm 2026</t>
+    <t xml:space="preserve">Kèm theo BBNT số: 19.NĐXB6A/CVXD ngày 07 tháng 09 năm 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Đắp đất nền đường lớp 2, độ chặt K&gt;=0,98 đoạn từ Km0+000,00 - Km0+126,46</t>
   </si>
   <si>
-    <t xml:space="preserve">Kèm theo BBNT số: 21.NĐXB6A/CVXD ngày 05 tháng 09 năm 2026</t>
+    <t xml:space="preserve">Kèm theo BBNT số: 21.NĐXB6A/CVXD ngày 08 tháng 09 năm 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Đắp cấp phối đá dăm loại 2 đoạn từ Km0+000,00 - Km0+126,46</t>
   </si>
   <si>
-    <t xml:space="preserve">Kèm theo BBNT số: 24.NĐXB6A/CVXD ngày 06 tháng 09 năm 2026</t>
+    <t xml:space="preserve">Kèm theo BBNT số: 24.NĐXB6A/CVXD ngày 09 tháng 09 năm 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Đắp cấp phối đá dăm loại 1 đoạn từ Km0+000,00 - Km0+126,46</t>
@@ -1397,7 +1397,7 @@
             <v xml:space="preserve">Kiểm tra cao độ đường đen đoạn từ Km0+000,00 -:- Km0+126,46</v>
           </cell>
           <cell r="D3" t="str">
-            <v xml:space="preserve">ngày 14 tháng 08 năm 2026</v>
+            <v xml:space="preserve">ngày 20 tháng 08 năm 2026</v>
           </cell>
           <cell r="G3" t="str">
             <v xml:space="preserve">01.NĐXB6A/CVXD </v>
@@ -1411,7 +1411,7 @@
             <v xml:space="preserve">Đào đất xử lý nền đường đoạn từ Km0+000,00 - Km0+126,46</v>
           </cell>
           <cell r="D4" t="str">
-            <v xml:space="preserve">ngày 15 tháng 08 năm 2026</v>
+            <v xml:space="preserve">ngày 24 tháng 08 năm 2026</v>
           </cell>
           <cell r="G4" t="str">
             <v xml:space="preserve">02.NĐXB6A/CVXD </v>
@@ -1425,7 +1425,7 @@
             <v xml:space="preserve">Rải vải địa kỹ thuật đoạn từ Km0+000,00 - Km0+126,46</v>
           </cell>
           <cell r="D5" t="str">
-            <v xml:space="preserve">ngày 15 tháng 08 năm 2026</v>
+            <v xml:space="preserve">ngày 24 tháng 08 năm 2026</v>
           </cell>
           <cell r="G5" t="str">
             <v xml:space="preserve">03.NĐXB6A/CVXD </v>
@@ -1439,7 +1439,7 @@
             <v xml:space="preserve">Đắp cát nền đường lớp 1 đoạn từ Km0+000,00 - Km0+126,46, độ chặt K&gt;=0,95</v>
           </cell>
           <cell r="D6" t="str">
-            <v xml:space="preserve">ngày 16 tháng 08 năm 2026</v>
+            <v xml:space="preserve">ngày 25 tháng 08 năm 2026</v>
           </cell>
           <cell r="G6" t="str">
             <v xml:space="preserve">04.NĐXB6A/CVXD </v>
@@ -1453,7 +1453,7 @@
             <v xml:space="preserve">Đắp cát nền đường lớp 2 đoạn từ Km0+000,00 - Km0+126,46, độ chặt K&gt;=0,95</v>
           </cell>
           <cell r="D7" t="str">
-            <v xml:space="preserve">ngày 17 tháng 08 năm 2026</v>
+            <v xml:space="preserve">ngày 26 tháng 08 năm 2026</v>
           </cell>
           <cell r="G7" t="str">
             <v xml:space="preserve">05.NĐXB6A/CVXD </v>
@@ -1467,7 +1467,7 @@
             <v xml:space="preserve">Đắp cát nền đường lớp 3 đoạn từ Km0+000,00 - Km0+126,46, độ chặt K&gt;=0,95</v>
           </cell>
           <cell r="D8" t="str">
-            <v xml:space="preserve">ngày 24 tháng 08 năm 2026</v>
+            <v xml:space="preserve">ngày 27 tháng 08 năm 2026</v>
           </cell>
           <cell r="G8" t="str">
             <v xml:space="preserve">06.NĐXB6A/CVXD </v>
@@ -1481,7 +1481,7 @@
             <v xml:space="preserve">Đắp cát nền đường lớp 4 đoạn từ Km0+000,00 - Km0+126,46, độ chặt K&gt;=0,95</v>
           </cell>
           <cell r="D9" t="str">
-            <v xml:space="preserve">ngày 25 tháng 08 năm 2026</v>
+            <v xml:space="preserve">ngày 28 tháng 08 năm 2026</v>
           </cell>
           <cell r="G9" t="str">
             <v xml:space="preserve">07.NĐXB6A/CVXD </v>
@@ -1495,7 +1495,7 @@
             <v xml:space="preserve">Đắp đất nền đường lớp 1 đoạn từ Km0+000,00 - Km0+126,46, độ chặt K&gt;=0,95</v>
           </cell>
           <cell r="D10" t="str">
-            <v xml:space="preserve">ngày 26 tháng 08 năm 2026</v>
+            <v xml:space="preserve">ngày 29 tháng 08 năm 2026</v>
           </cell>
           <cell r="G10" t="str">
             <v xml:space="preserve">08.NĐXB6A/CVXD </v>
@@ -1509,7 +1509,7 @@
             <v xml:space="preserve">Đắp đất nền đường lớp 2 đoạn từ Km0+000,00 - Km0+126,46, độ chặt K&gt;=0,95</v>
           </cell>
           <cell r="D11" t="str">
-            <v xml:space="preserve">ngày 26 tháng 08 năm 2026</v>
+            <v xml:space="preserve">ngày 29 tháng 08 năm 2026</v>
           </cell>
           <cell r="G11" t="str">
             <v xml:space="preserve">09.NĐXB6A/CVXD </v>
@@ -1523,7 +1523,7 @@
             <v xml:space="preserve">Đắp đất nền đường lớp 3 đoạn từ Km0+000,00 - Km0+126,46, độ chặt K&gt;=0,95</v>
           </cell>
           <cell r="D12" t="str">
-            <v xml:space="preserve">ngày 27 tháng 08 năm 2026</v>
+            <v xml:space="preserve">ngày 30 tháng 08 năm 2026</v>
           </cell>
           <cell r="G12" t="str">
             <v xml:space="preserve">10.NĐXB6A/CVXD </v>
@@ -1537,7 +1537,7 @@
             <v xml:space="preserve">Đắp đất nền đường lớp 4 đoạn từ Km0+000,00 - Km0+126,46, độ chặt K&gt;=0,95</v>
           </cell>
           <cell r="D13" t="str">
-            <v xml:space="preserve">ngày 27 tháng 08 năm 2026</v>
+            <v xml:space="preserve">ngày 30 tháng 08 năm 2026</v>
           </cell>
           <cell r="G13" t="str">
             <v xml:space="preserve">11.NĐXB6A/CVXD </v>
@@ -1551,7 +1551,7 @@
             <v xml:space="preserve">Đắp đất nền đường lớp 5 đoạn từ Km0+000,00 - Km0+126,46, độ chặt K&gt;=0,95</v>
           </cell>
           <cell r="D14" t="str">
-            <v xml:space="preserve">ngày 28 tháng 08 năm 2026</v>
+            <v xml:space="preserve">ngày 03 tháng 09 năm 2026</v>
           </cell>
           <cell r="G14" t="str">
             <v xml:space="preserve">12.NĐXB6A/CVXD </v>
@@ -1565,7 +1565,7 @@
             <v xml:space="preserve">Đắp đất nền đường lớp 6 đoạn từ Km0+000,00 - Km0+126,46, độ chặt K&gt;=0,95</v>
           </cell>
           <cell r="D15" t="str">
-            <v xml:space="preserve">ngày 28 tháng 08 năm 2026</v>
+            <v xml:space="preserve">ngày 03 tháng 09 năm 2026</v>
           </cell>
           <cell r="G15" t="str">
             <v xml:space="preserve">13.NĐXB6A/CVXD </v>
@@ -1579,7 +1579,7 @@
             <v xml:space="preserve">Đắp đất nền đường lớp 7 đoạn từ Km0+000,00 - Km0+126,46, độ chặt K&gt;=0,95</v>
           </cell>
           <cell r="D16" t="str">
-            <v xml:space="preserve">ngày 29 tháng 08 năm 2026</v>
+            <v xml:space="preserve">ngày 04 tháng 09 năm 2026</v>
           </cell>
           <cell r="G16" t="str">
             <v xml:space="preserve">14.NĐXB6A/CVXD </v>
@@ -1593,7 +1593,7 @@
             <v xml:space="preserve">Đắp đất nền đường lớp 8 đoạn từ Km0+000,00 - Km0+126,46, độ chặt K&gt;=0,95</v>
           </cell>
           <cell r="D17" t="str">
-            <v xml:space="preserve">ngày 29 tháng 08 năm 2026</v>
+            <v xml:space="preserve">ngày 04 tháng 09 năm 2026</v>
           </cell>
           <cell r="G17" t="str">
             <v xml:space="preserve">15.NĐXB6A/CVXD </v>
@@ -1607,7 +1607,7 @@
             <v xml:space="preserve">Đắp đất nền đường lớp 9 đoạn từ Km0+000,00 - Km0+126,46, độ chặt K&gt;=0,95</v>
           </cell>
           <cell r="D18" t="str">
-            <v xml:space="preserve">ngày 30 tháng 08 năm 2026</v>
+            <v xml:space="preserve">ngày 05 tháng 09 năm 2026</v>
           </cell>
           <cell r="G18" t="str">
             <v xml:space="preserve">16.NĐXB6A/CVXD </v>
@@ -1621,7 +1621,7 @@
             <v xml:space="preserve">Đắp đất nền đường lớp 1, độ chặt K&gt;=0,98 đoạn từ Km0+000,00 - Km0+126,46</v>
           </cell>
           <cell r="D19" t="str">
-            <v xml:space="preserve">ngày 03 tháng 09 năm 2026</v>
+            <v xml:space="preserve">ngày 06 tháng 09 năm 2026</v>
           </cell>
           <cell r="G19" t="str">
             <v xml:space="preserve">17.NĐXB6A/CVXD </v>
@@ -1635,7 +1635,7 @@
             <v xml:space="preserve">Đắp đất lề đường lớp 1, độ chặt K&gt;=0,95 đoạn từ Km0+000,00 - Km0+126,46</v>
           </cell>
           <cell r="D20" t="str">
-            <v xml:space="preserve">ngày 03 tháng 09 năm 2026</v>
+            <v xml:space="preserve">ngày 06 tháng 09 năm 2026</v>
           </cell>
           <cell r="G20" t="str">
             <v xml:space="preserve">18.NĐXB6A/CVXD </v>
@@ -1649,7 +1649,7 @@
             <v xml:space="preserve">Đắp đất nền đường lớp 2, độ chặt K&gt;=0,98 đoạn từ Km0+000,00 - Km0+126,46</v>
           </cell>
           <cell r="D21" t="str">
-            <v xml:space="preserve">ngày 04 tháng 09 năm 2026</v>
+            <v xml:space="preserve">ngày 07 tháng 09 năm 2026</v>
           </cell>
           <cell r="G21" t="str">
             <v xml:space="preserve">19.NĐXB6A/CVXD </v>
@@ -1663,7 +1663,7 @@
             <v xml:space="preserve">Đắp đất lề đường lớp 2, độ chặt K&gt;=0,95 đoạn từ Km0+000,00 - Km0+126,46</v>
           </cell>
           <cell r="D22" t="str">
-            <v xml:space="preserve">ngày 04 tháng 09 năm 2026</v>
+            <v xml:space="preserve">ngày 07 tháng 09 năm 2026</v>
           </cell>
           <cell r="G22" t="str">
             <v xml:space="preserve">20.NĐXB6A/CVXD </v>
@@ -1677,7 +1677,7 @@
             <v xml:space="preserve">Đắp cấp phối đá dăm loại 2 đoạn từ Km0+000,00 - Km0+126,46</v>
           </cell>
           <cell r="D23" t="str">
-            <v xml:space="preserve">ngày 05 tháng 09 năm 2026</v>
+            <v xml:space="preserve">ngày 08 tháng 09 năm 2026</v>
           </cell>
           <cell r="G23" t="str">
             <v xml:space="preserve">21.NĐXB6A/CVXD </v>
@@ -1691,7 +1691,7 @@
             <v xml:space="preserve">Đắp đất lề đường lớp 3, độ chặt K&gt;=0,95 đoạn từ Km0+000,00 - Km0+126,46</v>
           </cell>
           <cell r="D24" t="str">
-            <v xml:space="preserve">ngày 05 tháng 09 năm 2026</v>
+            <v xml:space="preserve">ngày 08 tháng 09 năm 2026</v>
           </cell>
           <cell r="G24" t="str">
             <v xml:space="preserve">22.NĐXB6A/CVXD </v>
@@ -1705,7 +1705,7 @@
             <v xml:space="preserve">Đắp đất lề đường lớp 4, độ chặt K&gt;=0,95 đoạn từ Km0+000,00 - Km0+126,46</v>
           </cell>
           <cell r="D25" t="str">
-            <v xml:space="preserve">ngày 06 tháng 09 năm 2026</v>
+            <v xml:space="preserve">ngày 09 tháng 09 năm 2026</v>
           </cell>
           <cell r="G25" t="str">
             <v xml:space="preserve">23.NĐXB6A/CVXD </v>
@@ -1719,7 +1719,7 @@
             <v xml:space="preserve">Đắp cấp phối đá dăm loại 1 đoạn từ Km0+000,00 - Km0+126,46</v>
           </cell>
           <cell r="D26" t="str">
-            <v xml:space="preserve">ngày 06 tháng 09 năm 2026</v>
+            <v xml:space="preserve">ngày 09 tháng 09 năm 2026</v>
           </cell>
           <cell r="G26" t="str">
             <v xml:space="preserve">24.NĐXB6A/CVXD </v>
@@ -1733,7 +1733,7 @@
             <v xml:space="preserve">Vệ sinh, thổi bụi mặt đường </v>
           </cell>
           <cell r="D27" t="str">
-            <v xml:space="preserve">ngày 08 tháng 09 năm 2026</v>
+            <v xml:space="preserve">ngày 11 tháng 09 năm 2026</v>
           </cell>
           <cell r="G27" t="str">
             <v xml:space="preserve">25.NĐXB6A/CVXD </v>
@@ -1747,7 +1747,7 @@
             <v xml:space="preserve">Tưới lớp thấm bám mặt đường, nhựa MC70, lượng nhựa 1kg/m2</v>
           </cell>
           <cell r="D28" t="str">
-            <v xml:space="preserve">ngày 10 tháng 09 năm 2026</v>
+            <v xml:space="preserve">ngày 13 tháng 09 năm 2026</v>
           </cell>
           <cell r="G28" t="str">
             <v xml:space="preserve">26.NĐXB6A/CVXD </v>
@@ -1761,7 +1761,7 @@
             <v xml:space="preserve">Rải thảm mặt đường bê tông nhựa C16 - Chiều dày mặt đường đã lèn ép 6cm</v>
           </cell>
           <cell r="D29" t="str">
-            <v xml:space="preserve">ngày 12 tháng 09 năm 2026</v>
+            <v xml:space="preserve">ngày 19 tháng 09 năm 2026</v>
           </cell>
           <cell r="G29" t="str">
             <v xml:space="preserve">27.NĐXB6A/CVXD </v>
@@ -1775,7 +1775,7 @@
             <v xml:space="preserve">Bê tông nhựa C16 - Chiều dày mặt đường đã lèn ép 6cm</v>
           </cell>
           <cell r="D30" t="str">
-            <v xml:space="preserve">ngày 19 tháng 09 năm 2026</v>
+            <v xml:space="preserve">ngày 21 tháng 09 năm 2026</v>
           </cell>
           <cell r="G30" t="str">
             <v xml:space="preserve">28.NĐXB6A/CVXD </v>
@@ -2021,7 +2021,7 @@
     <row r="2" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="str">
         <f>"Kèm theo BBNT số: "&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,7,0)&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,4,0)</f>
-        <v xml:space="preserve">Kèm theo BBNT số: 17.NĐXB6A/CVXD ngày 03 tháng 09 năm 2026</v>
+        <v xml:space="preserve">Kèm theo BBNT số: 17.NĐXB6A/CVXD ngày 06 tháng 09 năm 2026</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -2310,11 +2310,11 @@
       </c>
       <c r="E23" s="16" t="n">
         <f aca="false">+D23+F23</f>
-        <v>-3.7444</v>
+        <v>-3.7587</v>
       </c>
       <c r="F23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0056</v>
+        <v>-0.0087</v>
       </c>
       <c r="G23" s="16" t="n">
         <f aca="false">J23-3.45*2%-0.3*6%</f>
@@ -2322,11 +2322,11 @@
       </c>
       <c r="H23" s="16" t="n">
         <f aca="false">G23+I23</f>
-        <v>2.11</v>
+        <v>2.162</v>
       </c>
       <c r="I23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.018</v>
+        <v>0.07</v>
       </c>
       <c r="J23" s="16" t="n">
         <f aca="false">W23+0.25</f>
@@ -2334,22 +2334,22 @@
       </c>
       <c r="K23" s="16" t="n">
         <f aca="false">J23+L23</f>
-        <v>2.161</v>
+        <v>2.209</v>
       </c>
       <c r="L23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>-0.018</v>
+        <v>0.03</v>
       </c>
       <c r="M23" s="16" t="n">
         <v>3.75</v>
       </c>
       <c r="N23" s="16" t="n">
         <f aca="false">+M23+O23</f>
-        <v>3.7567</v>
+        <v>3.7497</v>
       </c>
       <c r="O23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0067</v>
+        <v>-0.0003</v>
       </c>
       <c r="P23" s="16" t="n">
         <f aca="false">G23</f>
@@ -2357,11 +2357,11 @@
       </c>
       <c r="Q23" s="16" t="n">
         <f aca="false">P23+R23</f>
-        <v>2.151</v>
+        <v>2.087</v>
       </c>
       <c r="R23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.059</v>
+        <v>-0.005</v>
       </c>
       <c r="S23" s="17"/>
       <c r="T23" s="18" t="n">
@@ -2388,11 +2388,11 @@
       </c>
       <c r="E24" s="16" t="n">
         <f aca="false">+D24+F24</f>
-        <v>-3.7571</v>
+        <v>-3.7581</v>
       </c>
       <c r="F24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0071</v>
+        <v>-0.0081</v>
       </c>
       <c r="G24" s="16" t="n">
         <f aca="false">J24-3.45*2%-0.3*6%</f>
@@ -2400,11 +2400,11 @@
       </c>
       <c r="H24" s="16" t="n">
         <f aca="false">G24+I24</f>
-        <v>2.101</v>
+        <v>2.111</v>
       </c>
       <c r="I24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.009</v>
+        <v>0.019</v>
       </c>
       <c r="J24" s="16" t="n">
         <f aca="false">W24+0.25</f>
@@ -2412,22 +2412,22 @@
       </c>
       <c r="K24" s="16" t="n">
         <f aca="false">J24+L24</f>
-        <v>2.204</v>
+        <v>2.194</v>
       </c>
       <c r="L24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.025</v>
+        <v>0.015</v>
       </c>
       <c r="M24" s="16" t="n">
         <v>3.75</v>
       </c>
       <c r="N24" s="16" t="n">
         <f aca="false">+M24+O24</f>
-        <v>3.7561</v>
+        <v>3.7527</v>
       </c>
       <c r="O24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0061</v>
+        <v>0.0027</v>
       </c>
       <c r="P24" s="16" t="n">
         <f aca="false">G24</f>
@@ -2435,11 +2435,11 @@
       </c>
       <c r="Q24" s="16" t="n">
         <f aca="false">P24+R24</f>
-        <v>2.146</v>
+        <v>2.13</v>
       </c>
       <c r="R24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.054</v>
+        <v>0.038</v>
       </c>
       <c r="S24" s="17"/>
       <c r="T24" s="18" t="n">
@@ -2466,11 +2466,11 @@
       </c>
       <c r="E25" s="16" t="n">
         <f aca="false">+D25+F25</f>
-        <v>-3.7395</v>
+        <v>-3.7401</v>
       </c>
       <c r="F25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0105</v>
+        <v>0.0099</v>
       </c>
       <c r="G25" s="16" t="n">
         <f aca="false">J25-3.45*2%-0.3*6%</f>
@@ -2478,11 +2478,11 @@
       </c>
       <c r="H25" s="16" t="n">
         <f aca="false">G25+I25</f>
-        <v>2.16</v>
+        <v>2.143</v>
       </c>
       <c r="I25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.06</v>
+        <v>0.043</v>
       </c>
       <c r="J25" s="16" t="n">
         <f aca="false">W25+0.25</f>
@@ -2490,22 +2490,22 @@
       </c>
       <c r="K25" s="16" t="n">
         <f aca="false">J25+L25</f>
-        <v>2.254</v>
+        <v>2.243</v>
       </c>
       <c r="L25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.067</v>
+        <v>0.056</v>
       </c>
       <c r="M25" s="16" t="n">
         <v>3.75</v>
       </c>
       <c r="N25" s="16" t="n">
         <f aca="false">+M25+O25</f>
-        <v>3.7509</v>
+        <v>3.7593</v>
       </c>
       <c r="O25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0009</v>
+        <v>0.0093</v>
       </c>
       <c r="P25" s="16" t="n">
         <f aca="false">G25</f>
@@ -2513,11 +2513,11 @@
       </c>
       <c r="Q25" s="16" t="n">
         <f aca="false">P25+R25</f>
-        <v>2.081</v>
+        <v>2.093</v>
       </c>
       <c r="R25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>-0.019</v>
+        <v>-0.007</v>
       </c>
       <c r="S25" s="17"/>
       <c r="T25" s="18" t="n">
@@ -2544,11 +2544,11 @@
       </c>
       <c r="E26" s="16" t="n">
         <f aca="false">+D26+F26</f>
-        <v>-3.7479</v>
+        <v>-3.7394</v>
       </c>
       <c r="F26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0021</v>
+        <v>0.0106</v>
       </c>
       <c r="G26" s="16" t="n">
         <f aca="false">J26-3.45*2%-0.3*6%</f>
@@ -2556,11 +2556,11 @@
       </c>
       <c r="H26" s="16" t="n">
         <f aca="false">G26+I26</f>
-        <v>2.174</v>
+        <v>2.096</v>
       </c>
       <c r="I26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.067</v>
+        <v>-0.011</v>
       </c>
       <c r="J26" s="16" t="n">
         <f aca="false">W26+0.25</f>
@@ -2568,22 +2568,22 @@
       </c>
       <c r="K26" s="16" t="n">
         <f aca="false">J26+L26</f>
-        <v>2.253</v>
+        <v>2.245</v>
       </c>
       <c r="L26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.059</v>
+        <v>0.051</v>
       </c>
       <c r="M26" s="16" t="n">
         <v>3.75</v>
       </c>
       <c r="N26" s="16" t="n">
         <f aca="false">+M26+O26</f>
-        <v>3.7464</v>
+        <v>3.7446</v>
       </c>
       <c r="O26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0036</v>
+        <v>-0.0054</v>
       </c>
       <c r="P26" s="16" t="n">
         <f aca="false">G26</f>
@@ -2591,11 +2591,11 @@
       </c>
       <c r="Q26" s="16" t="n">
         <f aca="false">P26+R26</f>
-        <v>2.143</v>
+        <v>2.129</v>
       </c>
       <c r="R26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.036</v>
+        <v>0.022</v>
       </c>
       <c r="S26" s="17"/>
       <c r="T26" s="18" t="n">
@@ -2622,11 +2622,11 @@
       </c>
       <c r="E27" s="16" t="n">
         <f aca="false">+D27+F27</f>
-        <v>-3.754</v>
+        <v>-3.7489</v>
       </c>
       <c r="F27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.004</v>
+        <v>0.0011</v>
       </c>
       <c r="G27" s="16" t="n">
         <f aca="false">J27-3.45*2%-0.3*6%</f>
@@ -2634,11 +2634,11 @@
       </c>
       <c r="H27" s="16" t="n">
         <f aca="false">G27+I27</f>
-        <v>2.13</v>
+        <v>2.166</v>
       </c>
       <c r="I27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.017</v>
+        <v>0.053</v>
       </c>
       <c r="J27" s="16" t="n">
         <f aca="false">W27+0.25</f>
@@ -2646,22 +2646,22 @@
       </c>
       <c r="K27" s="16" t="n">
         <f aca="false">J27+L27</f>
-        <v>2.2</v>
+        <v>2.254</v>
       </c>
       <c r="L27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0</v>
+        <v>0.054</v>
       </c>
       <c r="M27" s="16" t="n">
         <v>3.75</v>
       </c>
       <c r="N27" s="16" t="n">
         <f aca="false">+M27+O27</f>
-        <v>3.7501</v>
+        <v>3.7547</v>
       </c>
       <c r="O27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0001</v>
+        <v>0.0047</v>
       </c>
       <c r="P27" s="16" t="n">
         <f aca="false">G27</f>
@@ -2669,11 +2669,11 @@
       </c>
       <c r="Q27" s="16" t="n">
         <f aca="false">P27+R27</f>
-        <v>2.147</v>
+        <v>2.123</v>
       </c>
       <c r="R27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.034</v>
+        <v>0.01</v>
       </c>
       <c r="S27" s="17"/>
       <c r="T27" s="18" t="n">
@@ -2700,11 +2700,11 @@
       </c>
       <c r="E28" s="16" t="n">
         <f aca="false">+D28+F28</f>
-        <v>-3.7582</v>
+        <v>-3.7413</v>
       </c>
       <c r="F28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0082</v>
+        <v>0.0087</v>
       </c>
       <c r="G28" s="16" t="n">
         <f aca="false">J28-3.45*2%-0.3*6%</f>
@@ -2712,11 +2712,11 @@
       </c>
       <c r="H28" s="16" t="n">
         <f aca="false">G28+I28</f>
-        <v>2.144</v>
+        <v>2.128</v>
       </c>
       <c r="I28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.026</v>
+        <v>0.01</v>
       </c>
       <c r="J28" s="16" t="n">
         <f aca="false">W28+0.25</f>
@@ -2724,22 +2724,22 @@
       </c>
       <c r="K28" s="16" t="n">
         <f aca="false">J28+L28</f>
-        <v>2.212</v>
+        <v>2.27</v>
       </c>
       <c r="L28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.007</v>
+        <v>0.065</v>
       </c>
       <c r="M28" s="16" t="n">
         <v>3.75</v>
       </c>
       <c r="N28" s="16" t="n">
         <f aca="false">+M28+O28</f>
-        <v>3.7555</v>
+        <v>3.75</v>
       </c>
       <c r="O28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0055</v>
+        <v>0</v>
       </c>
       <c r="P28" s="16" t="n">
         <f aca="false">G28</f>
@@ -2747,11 +2747,11 @@
       </c>
       <c r="Q28" s="16" t="n">
         <f aca="false">P28+R28</f>
-        <v>2.111</v>
+        <v>2.168</v>
       </c>
       <c r="R28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>-0.007</v>
+        <v>0.05</v>
       </c>
       <c r="S28" s="17"/>
       <c r="T28" s="18" t="n">
@@ -2778,11 +2778,11 @@
       </c>
       <c r="E29" s="16" t="n">
         <f aca="false">+D29+F29</f>
-        <v>-3.759</v>
+        <v>-3.7428</v>
       </c>
       <c r="F29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.009</v>
+        <v>0.0072</v>
       </c>
       <c r="G29" s="16" t="n">
         <f aca="false">J29-3.45*2%-0.3*6%</f>
@@ -2790,11 +2790,11 @@
       </c>
       <c r="H29" s="16" t="n">
         <f aca="false">G29+I29</f>
-        <v>2.172</v>
+        <v>2.157</v>
       </c>
       <c r="I29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.045</v>
+        <v>0.03</v>
       </c>
       <c r="J29" s="16" t="n">
         <f aca="false">W29+0.25</f>
@@ -2802,22 +2802,22 @@
       </c>
       <c r="K29" s="16" t="n">
         <f aca="false">J29+L29</f>
-        <v>2.26</v>
+        <v>2.264</v>
       </c>
       <c r="L29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.046</v>
+        <v>0.05</v>
       </c>
       <c r="M29" s="16" t="n">
         <v>3.75</v>
       </c>
       <c r="N29" s="16" t="n">
         <f aca="false">+M29+O29</f>
-        <v>3.7462</v>
+        <v>3.7434</v>
       </c>
       <c r="O29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0038</v>
+        <v>-0.0066</v>
       </c>
       <c r="P29" s="16" t="n">
         <f aca="false">G29</f>
@@ -2825,11 +2825,11 @@
       </c>
       <c r="Q29" s="16" t="n">
         <f aca="false">P29+R29</f>
-        <v>2.151</v>
+        <v>2.171</v>
       </c>
       <c r="R29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.024</v>
+        <v>0.044</v>
       </c>
       <c r="S29" s="17"/>
       <c r="T29" s="18" t="n">
@@ -2856,11 +2856,11 @@
       </c>
       <c r="E30" s="16" t="n">
         <f aca="false">+D30+F30</f>
-        <v>-3.7434</v>
+        <v>-3.752</v>
       </c>
       <c r="F30" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0066</v>
+        <v>-0.002</v>
       </c>
       <c r="G30" s="16" t="n">
         <f aca="false">J30-3.45*2%-0.3*6%</f>
@@ -2868,11 +2868,11 @@
       </c>
       <c r="H30" s="16" t="n">
         <f aca="false">G30+I30</f>
-        <v>2.158</v>
+        <v>2.183</v>
       </c>
       <c r="I30" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.022</v>
+        <v>0.047</v>
       </c>
       <c r="J30" s="16" t="n">
         <f aca="false">W30+0.25</f>
@@ -2880,22 +2880,22 @@
       </c>
       <c r="K30" s="16" t="n">
         <f aca="false">J30+L30</f>
-        <v>2.207</v>
+        <v>2.223</v>
       </c>
       <c r="L30" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>-0.016</v>
+        <v>0</v>
       </c>
       <c r="M30" s="16" t="n">
         <v>3.75</v>
       </c>
       <c r="N30" s="16" t="n">
         <f aca="false">+M30+O30</f>
-        <v>3.7608</v>
+        <v>3.7597</v>
       </c>
       <c r="O30" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0108</v>
+        <v>0.0097</v>
       </c>
       <c r="P30" s="16" t="n">
         <f aca="false">G30</f>
@@ -2934,11 +2934,11 @@
       </c>
       <c r="E31" s="16" t="n">
         <f aca="false">+D31+F31</f>
-        <v>-3.7405</v>
+        <v>-3.7484</v>
       </c>
       <c r="F31" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0095</v>
+        <v>0.0016</v>
       </c>
       <c r="G31" s="16" t="n">
         <f aca="false">J31-3.45*2%-0.3*6%</f>
@@ -2946,11 +2946,11 @@
       </c>
       <c r="H31" s="16" t="n">
         <f aca="false">G31+I31</f>
-        <v>2.206</v>
+        <v>2.204</v>
       </c>
       <c r="I31" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.07</v>
+        <v>0.068</v>
       </c>
       <c r="J31" s="16" t="n">
         <f aca="false">W31+0.25</f>
@@ -2958,22 +2958,22 @@
       </c>
       <c r="K31" s="16" t="n">
         <f aca="false">J31+L31</f>
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="L31" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.007</v>
+        <v>-0.013</v>
       </c>
       <c r="M31" s="16" t="n">
         <v>3.75</v>
       </c>
       <c r="N31" s="16" t="n">
         <f aca="false">+M31+O31</f>
-        <v>3.7442</v>
+        <v>3.741</v>
       </c>
       <c r="O31" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0058</v>
+        <v>-0.009</v>
       </c>
       <c r="P31" s="16" t="n">
         <f aca="false">G31</f>
@@ -2981,11 +2981,11 @@
       </c>
       <c r="Q31" s="16" t="n">
         <f aca="false">P31+R31</f>
-        <v>2.172</v>
+        <v>2.178</v>
       </c>
       <c r="R31" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.036</v>
+        <v>0.042</v>
       </c>
       <c r="S31" s="17"/>
       <c r="T31" s="18"/>
@@ -3190,7 +3190,7 @@
     <row r="2" s="27" customFormat="true" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="str">
         <f>"Kèm theo BBNT số: "&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,7,0)&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,4,0)</f>
-        <v xml:space="preserve">Kèm theo BBNT số: 17.NĐXB6A/CVXD ngày 03 tháng 09 năm 2026</v>
+        <v xml:space="preserve">Kèm theo BBNT số: 17.NĐXB6A/CVXD ngày 06 tháng 09 năm 2026</v>
       </c>
       <c r="B2" s="28"/>
       <c r="C2" s="28"/>
@@ -8410,7 +8410,7 @@
     <row r="2" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="str">
         <f>"Kèm theo BBNT số: "&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,7,0)&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,4,0)</f>
-        <v xml:space="preserve">Kèm theo BBNT số: 19.NĐXB6A/CVXD ngày 04 tháng 09 năm 2026</v>
+        <v xml:space="preserve">Kèm theo BBNT số: 19.NĐXB6A/CVXD ngày 07 tháng 09 năm 2026</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -8696,11 +8696,11 @@
       </c>
       <c r="E23" s="16" t="n">
         <f aca="false">+D23+F23</f>
-        <v>-3.7566</v>
+        <v>-3.7576</v>
       </c>
       <c r="F23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0066</v>
+        <v>-0.0076</v>
       </c>
       <c r="G23" s="16" t="n">
         <f aca="false">W23+0.25</f>
@@ -8708,11 +8708,11 @@
       </c>
       <c r="H23" s="16" t="n">
         <f aca="false">G23+I23</f>
-        <v>2.384</v>
+        <v>2.395</v>
       </c>
       <c r="I23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.042</v>
+        <v>0.053</v>
       </c>
       <c r="J23" s="16" t="n">
         <f aca="false">X23+0.25</f>
@@ -8720,22 +8720,22 @@
       </c>
       <c r="K23" s="16" t="n">
         <f aca="false">J23+L23</f>
-        <v>2.468</v>
+        <v>2.492</v>
       </c>
       <c r="L23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.039</v>
+        <v>0.063</v>
       </c>
       <c r="M23" s="16" t="n">
         <v>3.75</v>
       </c>
       <c r="N23" s="16" t="n">
         <f aca="false">+M23+O23</f>
-        <v>3.7579</v>
+        <v>3.7519</v>
       </c>
       <c r="O23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0079</v>
+        <v>0.0019</v>
       </c>
       <c r="P23" s="16" t="n">
         <f aca="false">Y23+0.25</f>
@@ -8743,11 +8743,11 @@
       </c>
       <c r="Q23" s="16" t="n">
         <f aca="false">P23+R23</f>
-        <v>2.398</v>
+        <v>2.387</v>
       </c>
       <c r="R23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.056</v>
+        <v>0.045</v>
       </c>
       <c r="S23" s="17"/>
       <c r="T23" s="18" t="n">
@@ -8783,11 +8783,11 @@
       </c>
       <c r="E24" s="16" t="n">
         <f aca="false">+D24+F24</f>
-        <v>-3.7407</v>
+        <v>-3.7534</v>
       </c>
       <c r="F24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0093</v>
+        <v>-0.0034</v>
       </c>
       <c r="G24" s="16" t="n">
         <f aca="false">W24+0.25</f>
@@ -8795,11 +8795,11 @@
       </c>
       <c r="H24" s="16" t="n">
         <f aca="false">G24+I24</f>
-        <v>2.356</v>
+        <v>2.386</v>
       </c>
       <c r="I24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.014</v>
+        <v>0.044</v>
       </c>
       <c r="J24" s="16" t="n">
         <f aca="false">X24+0.25</f>
@@ -8807,22 +8807,22 @@
       </c>
       <c r="K24" s="16" t="n">
         <f aca="false">J24+L24</f>
-        <v>2.472</v>
+        <v>2.471</v>
       </c>
       <c r="L24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.043</v>
+        <v>0.042</v>
       </c>
       <c r="M24" s="16" t="n">
         <v>3.75</v>
       </c>
       <c r="N24" s="16" t="n">
         <f aca="false">+M24+O24</f>
-        <v>3.7478</v>
+        <v>3.7438</v>
       </c>
       <c r="O24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0022</v>
+        <v>-0.0062</v>
       </c>
       <c r="P24" s="16" t="n">
         <f aca="false">Y24+0.25</f>
@@ -8830,11 +8830,11 @@
       </c>
       <c r="Q24" s="16" t="n">
         <f aca="false">P24+R24</f>
-        <v>2.358</v>
+        <v>2.399</v>
       </c>
       <c r="R24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.016</v>
+        <v>0.057</v>
       </c>
       <c r="S24" s="17"/>
       <c r="T24" s="18" t="n">
@@ -8870,11 +8870,11 @@
       </c>
       <c r="E25" s="16" t="n">
         <f aca="false">+D25+F25</f>
-        <v>-3.7426</v>
+        <v>-3.7537</v>
       </c>
       <c r="F25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0074</v>
+        <v>-0.0037</v>
       </c>
       <c r="G25" s="16" t="n">
         <f aca="false">W25+0.25</f>
@@ -8882,11 +8882,11 @@
       </c>
       <c r="H25" s="16" t="n">
         <f aca="false">G25+I25</f>
-        <v>2.42</v>
+        <v>2.344</v>
       </c>
       <c r="I25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.07</v>
+        <v>-0.006</v>
       </c>
       <c r="J25" s="16" t="n">
         <f aca="false">X25+0.25</f>
@@ -8894,22 +8894,22 @@
       </c>
       <c r="K25" s="16" t="n">
         <f aca="false">J25+L25</f>
-        <v>2.435</v>
+        <v>2.492</v>
       </c>
       <c r="L25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>-0.002</v>
+        <v>0.055</v>
       </c>
       <c r="M25" s="16" t="n">
         <v>3.75</v>
       </c>
       <c r="N25" s="16" t="n">
         <f aca="false">+M25+O25</f>
-        <v>3.7541</v>
+        <v>3.7452</v>
       </c>
       <c r="O25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0041</v>
+        <v>-0.0048</v>
       </c>
       <c r="P25" s="16" t="n">
         <f aca="false">Y25+0.25</f>
@@ -8917,11 +8917,11 @@
       </c>
       <c r="Q25" s="16" t="n">
         <f aca="false">P25+R25</f>
-        <v>2.375</v>
+        <v>2.338</v>
       </c>
       <c r="R25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.025</v>
+        <v>-0.012</v>
       </c>
       <c r="S25" s="17"/>
       <c r="T25" s="18" t="n">
@@ -8957,11 +8957,11 @@
       </c>
       <c r="E26" s="16" t="n">
         <f aca="false">+D26+F26</f>
-        <v>-3.7506</v>
+        <v>-3.7445</v>
       </c>
       <c r="F26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0006</v>
+        <v>0.0055</v>
       </c>
       <c r="G26" s="16" t="n">
         <f aca="false">W26+0.25</f>
@@ -8969,11 +8969,11 @@
       </c>
       <c r="H26" s="16" t="n">
         <f aca="false">G26+I26</f>
-        <v>2.374</v>
+        <v>2.387</v>
       </c>
       <c r="I26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.017</v>
+        <v>0.03</v>
       </c>
       <c r="J26" s="16" t="n">
         <f aca="false">X26+0.25</f>
@@ -8981,22 +8981,22 @@
       </c>
       <c r="K26" s="16" t="n">
         <f aca="false">J26+L26</f>
-        <v>2.43</v>
+        <v>2.465</v>
       </c>
       <c r="L26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>-0.014</v>
+        <v>0.021</v>
       </c>
       <c r="M26" s="16" t="n">
         <v>3.75</v>
       </c>
       <c r="N26" s="16" t="n">
         <f aca="false">+M26+O26</f>
-        <v>3.7431</v>
+        <v>3.7414</v>
       </c>
       <c r="O26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0069</v>
+        <v>-0.0086</v>
       </c>
       <c r="P26" s="16" t="n">
         <f aca="false">Y26+0.25</f>
@@ -9004,11 +9004,11 @@
       </c>
       <c r="Q26" s="16" t="n">
         <f aca="false">P26+R26</f>
-        <v>2.413</v>
+        <v>2.357</v>
       </c>
       <c r="R26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.056</v>
+        <v>0</v>
       </c>
       <c r="S26" s="17"/>
       <c r="T26" s="18" t="n">
@@ -9044,11 +9044,11 @@
       </c>
       <c r="E27" s="16" t="n">
         <f aca="false">+D27+F27</f>
-        <v>-3.7498</v>
+        <v>-3.7566</v>
       </c>
       <c r="F27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0002</v>
+        <v>-0.0066</v>
       </c>
       <c r="G27" s="16" t="n">
         <f aca="false">W27+0.25</f>
@@ -9056,11 +9056,11 @@
       </c>
       <c r="H27" s="16" t="n">
         <f aca="false">G27+I27</f>
-        <v>2.356</v>
+        <v>2.36</v>
       </c>
       <c r="I27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>-0.007</v>
+        <v>-0.003</v>
       </c>
       <c r="J27" s="16" t="n">
         <f aca="false">X27+0.25</f>
@@ -9068,22 +9068,22 @@
       </c>
       <c r="K27" s="16" t="n">
         <f aca="false">J27+L27</f>
-        <v>2.512</v>
+        <v>2.467</v>
       </c>
       <c r="L27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.062</v>
+        <v>0.017</v>
       </c>
       <c r="M27" s="16" t="n">
         <v>3.75</v>
       </c>
       <c r="N27" s="16" t="n">
         <f aca="false">+M27+O27</f>
-        <v>3.7454</v>
+        <v>3.7459</v>
       </c>
       <c r="O27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0046</v>
+        <v>-0.0041</v>
       </c>
       <c r="P27" s="16" t="n">
         <f aca="false">Y27+0.25</f>
@@ -9091,11 +9091,11 @@
       </c>
       <c r="Q27" s="16" t="n">
         <f aca="false">P27+R27</f>
-        <v>2.355</v>
+        <v>2.35</v>
       </c>
       <c r="R27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>-0.008</v>
+        <v>-0.013</v>
       </c>
       <c r="S27" s="17"/>
       <c r="T27" s="18" t="n">
@@ -9131,11 +9131,11 @@
       </c>
       <c r="E28" s="16" t="n">
         <f aca="false">+D28+F28</f>
-        <v>-3.7531</v>
+        <v>-3.7566</v>
       </c>
       <c r="F28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0031</v>
+        <v>-0.0066</v>
       </c>
       <c r="G28" s="16" t="n">
         <f aca="false">W28+0.25</f>
@@ -9143,11 +9143,11 @@
       </c>
       <c r="H28" s="16" t="n">
         <f aca="false">G28+I28</f>
-        <v>2.37</v>
+        <v>2.418</v>
       </c>
       <c r="I28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.002</v>
+        <v>0.05</v>
       </c>
       <c r="J28" s="16" t="n">
         <f aca="false">X28+0.25</f>
@@ -9155,22 +9155,22 @@
       </c>
       <c r="K28" s="16" t="n">
         <f aca="false">J28+L28</f>
-        <v>2.465</v>
+        <v>2.52</v>
       </c>
       <c r="L28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.01</v>
+        <v>0.065</v>
       </c>
       <c r="M28" s="16" t="n">
         <v>3.75</v>
       </c>
       <c r="N28" s="16" t="n">
         <f aca="false">+M28+O28</f>
-        <v>3.7513</v>
+        <v>3.7403</v>
       </c>
       <c r="O28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0013</v>
+        <v>-0.0097</v>
       </c>
       <c r="P28" s="16" t="n">
         <f aca="false">Y28+0.25</f>
@@ -9178,11 +9178,11 @@
       </c>
       <c r="Q28" s="16" t="n">
         <f aca="false">P28+R28</f>
-        <v>2.362</v>
+        <v>2.39</v>
       </c>
       <c r="R28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>-0.006</v>
+        <v>0.022</v>
       </c>
       <c r="S28" s="17"/>
       <c r="T28" s="18" t="n">
@@ -9218,11 +9218,11 @@
       </c>
       <c r="E29" s="16" t="n">
         <f aca="false">+D29+F29</f>
-        <v>-3.7419</v>
+        <v>-3.7459</v>
       </c>
       <c r="F29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0081</v>
+        <v>0.0041</v>
       </c>
       <c r="G29" s="16" t="n">
         <f aca="false">W29+0.25</f>
@@ -9230,11 +9230,11 @@
       </c>
       <c r="H29" s="16" t="n">
         <f aca="false">G29+I29</f>
-        <v>2.396</v>
+        <v>2.36</v>
       </c>
       <c r="I29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.019</v>
+        <v>-0.017</v>
       </c>
       <c r="J29" s="16" t="n">
         <f aca="false">X29+0.25</f>
@@ -9242,22 +9242,22 @@
       </c>
       <c r="K29" s="16" t="n">
         <f aca="false">J29+L29</f>
-        <v>2.458</v>
+        <v>2.502</v>
       </c>
       <c r="L29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>-0.006</v>
+        <v>0.038</v>
       </c>
       <c r="M29" s="16" t="n">
         <v>3.75</v>
       </c>
       <c r="N29" s="16" t="n">
         <f aca="false">+M29+O29</f>
-        <v>3.7578</v>
+        <v>3.753</v>
       </c>
       <c r="O29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0078</v>
+        <v>0.003</v>
       </c>
       <c r="P29" s="16" t="n">
         <f aca="false">Y29+0.25</f>
@@ -9265,11 +9265,11 @@
       </c>
       <c r="Q29" s="16" t="n">
         <f aca="false">P29+R29</f>
-        <v>2.374</v>
+        <v>2.382</v>
       </c>
       <c r="R29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>-0.003</v>
+        <v>0.005</v>
       </c>
       <c r="S29" s="17"/>
       <c r="T29" s="18" t="n">
@@ -9305,11 +9305,11 @@
       </c>
       <c r="E30" s="16" t="n">
         <f aca="false">+D30+F30</f>
-        <v>-3.741</v>
+        <v>-3.7593</v>
       </c>
       <c r="F30" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.009</v>
+        <v>-0.0093</v>
       </c>
       <c r="G30" s="16" t="n">
         <f aca="false">W30+0.25</f>
@@ -9317,11 +9317,11 @@
       </c>
       <c r="H30" s="16" t="n">
         <f aca="false">G30+I30</f>
-        <v>2.449</v>
+        <v>2.389</v>
       </c>
       <c r="I30" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.063</v>
+        <v>0.003</v>
       </c>
       <c r="J30" s="16" t="n">
         <f aca="false">X30+0.25</f>
@@ -9329,22 +9329,22 @@
       </c>
       <c r="K30" s="16" t="n">
         <f aca="false">J30+L30</f>
-        <v>2.522</v>
+        <v>2.488</v>
       </c>
       <c r="L30" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.049</v>
+        <v>0.015</v>
       </c>
       <c r="M30" s="16" t="n">
         <v>3.75</v>
       </c>
       <c r="N30" s="16" t="n">
         <f aca="false">+M30+O30</f>
-        <v>3.7511</v>
+        <v>3.7518</v>
       </c>
       <c r="O30" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0011</v>
+        <v>0.0018</v>
       </c>
       <c r="P30" s="16" t="n">
         <f aca="false">Y30+0.25</f>
@@ -9352,11 +9352,11 @@
       </c>
       <c r="Q30" s="16" t="n">
         <f aca="false">P30+R30</f>
-        <v>2.415</v>
+        <v>2.37</v>
       </c>
       <c r="R30" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.029</v>
+        <v>-0.016</v>
       </c>
       <c r="S30" s="17"/>
       <c r="T30" s="18" t="n">
@@ -9392,11 +9392,11 @@
       </c>
       <c r="E31" s="16" t="n">
         <f aca="false">+D31+F31</f>
-        <v>-3.7434</v>
+        <v>-3.7494</v>
       </c>
       <c r="F31" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0066</v>
+        <v>0.0006</v>
       </c>
       <c r="G31" s="16" t="n">
         <f aca="false">W31+0.25</f>
@@ -9404,11 +9404,11 @@
       </c>
       <c r="H31" s="16" t="n">
         <f aca="false">G31+I31</f>
-        <v>2.441</v>
+        <v>2.401</v>
       </c>
       <c r="I31" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.055</v>
+        <v>0.015</v>
       </c>
       <c r="J31" s="16" t="n">
         <f aca="false">X31+0.25</f>
@@ -9416,22 +9416,22 @@
       </c>
       <c r="K31" s="16" t="n">
         <f aca="false">J31+L31</f>
-        <v>2.463</v>
+        <v>2.515</v>
       </c>
       <c r="L31" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>-0.01</v>
+        <v>0.042</v>
       </c>
       <c r="M31" s="16" t="n">
         <v>3.75</v>
       </c>
       <c r="N31" s="16" t="n">
         <f aca="false">+M31+O31</f>
-        <v>3.7444</v>
+        <v>3.7401</v>
       </c>
       <c r="O31" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0056</v>
+        <v>-0.0099</v>
       </c>
       <c r="P31" s="16" t="n">
         <f aca="false">Y31+0.25</f>
@@ -9439,11 +9439,11 @@
       </c>
       <c r="Q31" s="16" t="n">
         <f aca="false">P31+R31</f>
-        <v>2.367</v>
+        <v>2.414</v>
       </c>
       <c r="R31" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>-0.019</v>
+        <v>0.028</v>
       </c>
       <c r="S31" s="17"/>
       <c r="T31" s="18"/>
@@ -9657,7 +9657,7 @@
     <row r="2" s="27" customFormat="true" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="str">
         <f>"Kèm theo BBNT số: "&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,7,0)&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,4,0)</f>
-        <v xml:space="preserve">Kèm theo BBNT số: 19.NĐXB6A/CVXD ngày 04 tháng 09 năm 2026</v>
+        <v xml:space="preserve">Kèm theo BBNT số: 19.NĐXB6A/CVXD ngày 07 tháng 09 năm 2026</v>
       </c>
       <c r="B2" s="28"/>
       <c r="C2" s="28"/>
@@ -14851,7 +14851,7 @@
     <row r="2" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="str">
         <f>"Kèm theo BBNT số: "&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,7,0)&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,4,0)</f>
-        <v xml:space="preserve">Kèm theo BBNT số: 21.NĐXB6A/CVXD ngày 05 tháng 09 năm 2026</v>
+        <v xml:space="preserve">Kèm theo BBNT số: 21.NĐXB6A/CVXD ngày 08 tháng 09 năm 2026</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -15137,11 +15137,11 @@
       </c>
       <c r="E23" s="16" t="n">
         <f aca="false">+D23+F23</f>
-        <v>-3.7598</v>
+        <v>-3.7583</v>
       </c>
       <c r="F23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0098</v>
+        <v>-0.0083</v>
       </c>
       <c r="G23" s="16" t="n">
         <f aca="false">W23+0.18</f>
@@ -15149,11 +15149,11 @@
       </c>
       <c r="H23" s="16" t="n">
         <f aca="false">G23+I23</f>
-        <v>2.579</v>
+        <v>2.592</v>
       </c>
       <c r="I23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.057</v>
+        <v>0.07</v>
       </c>
       <c r="J23" s="16" t="n">
         <f aca="false">X23+0.18</f>
@@ -15161,22 +15161,22 @@
       </c>
       <c r="K23" s="16" t="n">
         <f aca="false">J23+L23</f>
-        <v>2.635</v>
+        <v>2.654</v>
       </c>
       <c r="L23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.026</v>
+        <v>0.045</v>
       </c>
       <c r="M23" s="16" t="n">
         <v>3.75</v>
       </c>
       <c r="N23" s="16" t="n">
         <f aca="false">+M23+O23</f>
-        <v>3.7542</v>
+        <v>3.7533</v>
       </c>
       <c r="O23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0042</v>
+        <v>0.0033</v>
       </c>
       <c r="P23" s="16" t="n">
         <f aca="false">Y23+0.18</f>
@@ -15184,11 +15184,11 @@
       </c>
       <c r="Q23" s="16" t="n">
         <f aca="false">P23+R23</f>
-        <v>2.527</v>
+        <v>2.511</v>
       </c>
       <c r="R23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.005</v>
+        <v>-0.011</v>
       </c>
       <c r="S23" s="17"/>
       <c r="T23" s="18" t="n">
@@ -15224,11 +15224,11 @@
       </c>
       <c r="E24" s="16" t="n">
         <f aca="false">+D24+F24</f>
-        <v>-3.7525</v>
+        <v>-3.7537</v>
       </c>
       <c r="F24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0025</v>
+        <v>-0.0037</v>
       </c>
       <c r="G24" s="16" t="n">
         <f aca="false">W24+0.18</f>
@@ -15236,11 +15236,11 @@
       </c>
       <c r="H24" s="16" t="n">
         <f aca="false">G24+I24</f>
-        <v>2.558</v>
+        <v>2.566</v>
       </c>
       <c r="I24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.036</v>
+        <v>0.044</v>
       </c>
       <c r="J24" s="16" t="n">
         <f aca="false">X24+0.18</f>
@@ -15248,22 +15248,22 @@
       </c>
       <c r="K24" s="16" t="n">
         <f aca="false">J24+L24</f>
-        <v>2.606</v>
+        <v>2.629</v>
       </c>
       <c r="L24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>-0.003</v>
+        <v>0.02</v>
       </c>
       <c r="M24" s="16" t="n">
         <v>3.75</v>
       </c>
       <c r="N24" s="16" t="n">
         <f aca="false">+M24+O24</f>
-        <v>3.7567</v>
+        <v>3.7584</v>
       </c>
       <c r="O24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0067</v>
+        <v>0.0084</v>
       </c>
       <c r="P24" s="16" t="n">
         <f aca="false">Y24+0.18</f>
@@ -15271,11 +15271,11 @@
       </c>
       <c r="Q24" s="16" t="n">
         <f aca="false">P24+R24</f>
-        <v>2.57</v>
+        <v>2.551</v>
       </c>
       <c r="R24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.048</v>
+        <v>0.029</v>
       </c>
       <c r="S24" s="17"/>
       <c r="T24" s="18" t="n">
@@ -15311,11 +15311,11 @@
       </c>
       <c r="E25" s="16" t="n">
         <f aca="false">+D25+F25</f>
-        <v>-3.7436</v>
+        <v>-3.7504</v>
       </c>
       <c r="F25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0064</v>
+        <v>-0.0004</v>
       </c>
       <c r="G25" s="16" t="n">
         <f aca="false">W25+0.18</f>
@@ -15323,11 +15323,11 @@
       </c>
       <c r="H25" s="16" t="n">
         <f aca="false">G25+I25</f>
-        <v>2.527</v>
+        <v>2.551</v>
       </c>
       <c r="I25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>-0.003</v>
+        <v>0.021</v>
       </c>
       <c r="J25" s="16" t="n">
         <f aca="false">X25+0.18</f>
@@ -15335,22 +15335,22 @@
       </c>
       <c r="K25" s="16" t="n">
         <f aca="false">J25+L25</f>
-        <v>2.659</v>
+        <v>2.653</v>
       </c>
       <c r="L25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.042</v>
+        <v>0.036</v>
       </c>
       <c r="M25" s="16" t="n">
         <v>3.75</v>
       </c>
       <c r="N25" s="16" t="n">
         <f aca="false">+M25+O25</f>
-        <v>3.754</v>
+        <v>3.7559</v>
       </c>
       <c r="O25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.004</v>
+        <v>0.0059</v>
       </c>
       <c r="P25" s="16" t="n">
         <f aca="false">Y25+0.18</f>
@@ -15358,11 +15358,11 @@
       </c>
       <c r="Q25" s="16" t="n">
         <f aca="false">P25+R25</f>
-        <v>2.549</v>
+        <v>2.528</v>
       </c>
       <c r="R25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.019</v>
+        <v>-0.002</v>
       </c>
       <c r="S25" s="17"/>
       <c r="T25" s="18" t="n">
@@ -15398,11 +15398,11 @@
       </c>
       <c r="E26" s="16" t="n">
         <f aca="false">+D26+F26</f>
-        <v>-3.7469</v>
+        <v>-3.7511</v>
       </c>
       <c r="F26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0031</v>
+        <v>-0.0011</v>
       </c>
       <c r="G26" s="16" t="n">
         <f aca="false">W26+0.18</f>
@@ -15410,11 +15410,11 @@
       </c>
       <c r="H26" s="16" t="n">
         <f aca="false">G26+I26</f>
-        <v>2.593</v>
+        <v>2.606</v>
       </c>
       <c r="I26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.056</v>
+        <v>0.069</v>
       </c>
       <c r="J26" s="16" t="n">
         <f aca="false">X26+0.18</f>
@@ -15422,22 +15422,22 @@
       </c>
       <c r="K26" s="16" t="n">
         <f aca="false">J26+L26</f>
-        <v>2.631</v>
+        <v>2.604</v>
       </c>
       <c r="L26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.007</v>
+        <v>-0.02</v>
       </c>
       <c r="M26" s="16" t="n">
         <v>3.75</v>
       </c>
       <c r="N26" s="16" t="n">
         <f aca="false">+M26+O26</f>
-        <v>3.7559</v>
+        <v>3.7566</v>
       </c>
       <c r="O26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0059</v>
+        <v>0.0066</v>
       </c>
       <c r="P26" s="16" t="n">
         <f aca="false">Y26+0.18</f>
@@ -15445,11 +15445,11 @@
       </c>
       <c r="Q26" s="16" t="n">
         <f aca="false">P26+R26</f>
-        <v>2.553</v>
+        <v>2.577</v>
       </c>
       <c r="R26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.016</v>
+        <v>0.04</v>
       </c>
       <c r="S26" s="17"/>
       <c r="T26" s="18" t="n">
@@ -15485,11 +15485,11 @@
       </c>
       <c r="E27" s="16" t="n">
         <f aca="false">+D27+F27</f>
-        <v>-3.7539</v>
+        <v>-3.7566</v>
       </c>
       <c r="F27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0039</v>
+        <v>-0.0066</v>
       </c>
       <c r="G27" s="16" t="n">
         <f aca="false">W27+0.18</f>
@@ -15497,11 +15497,11 @@
       </c>
       <c r="H27" s="16" t="n">
         <f aca="false">G27+I27</f>
-        <v>2.612</v>
+        <v>2.535</v>
       </c>
       <c r="I27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.069</v>
+        <v>-0.008</v>
       </c>
       <c r="J27" s="16" t="n">
         <f aca="false">X27+0.18</f>
@@ -15509,22 +15509,22 @@
       </c>
       <c r="K27" s="16" t="n">
         <f aca="false">J27+L27</f>
-        <v>2.616</v>
+        <v>2.632</v>
       </c>
       <c r="L27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>-0.014</v>
+        <v>0.002</v>
       </c>
       <c r="M27" s="16" t="n">
         <v>3.75</v>
       </c>
       <c r="N27" s="16" t="n">
         <f aca="false">+M27+O27</f>
-        <v>3.7518</v>
+        <v>3.7438</v>
       </c>
       <c r="O27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0018</v>
+        <v>-0.0062</v>
       </c>
       <c r="P27" s="16" t="n">
         <f aca="false">Y27+0.18</f>
@@ -15532,11 +15532,11 @@
       </c>
       <c r="Q27" s="16" t="n">
         <f aca="false">P27+R27</f>
-        <v>2.527</v>
+        <v>2.551</v>
       </c>
       <c r="R27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>-0.016</v>
+        <v>0.008</v>
       </c>
       <c r="S27" s="17"/>
       <c r="T27" s="18" t="n">
@@ -15572,11 +15572,11 @@
       </c>
       <c r="E28" s="16" t="n">
         <f aca="false">+D28+F28</f>
-        <v>-3.7388</v>
+        <v>-3.7477</v>
       </c>
       <c r="F28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0112</v>
+        <v>0.0023</v>
       </c>
       <c r="G28" s="16" t="n">
         <f aca="false">W28+0.18</f>
@@ -15584,11 +15584,11 @@
       </c>
       <c r="H28" s="16" t="n">
         <f aca="false">G28+I28</f>
-        <v>2.612</v>
+        <v>2.557</v>
       </c>
       <c r="I28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.064</v>
+        <v>0.009</v>
       </c>
       <c r="J28" s="16" t="n">
         <f aca="false">X28+0.18</f>
@@ -15596,22 +15596,22 @@
       </c>
       <c r="K28" s="16" t="n">
         <f aca="false">J28+L28</f>
-        <v>2.621</v>
+        <v>2.65</v>
       </c>
       <c r="L28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>-0.014</v>
+        <v>0.015</v>
       </c>
       <c r="M28" s="16" t="n">
         <v>3.75</v>
       </c>
       <c r="N28" s="16" t="n">
         <f aca="false">+M28+O28</f>
-        <v>3.7549</v>
+        <v>3.7556</v>
       </c>
       <c r="O28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0049</v>
+        <v>0.0056</v>
       </c>
       <c r="P28" s="16" t="n">
         <f aca="false">Y28+0.18</f>
@@ -15619,11 +15619,11 @@
       </c>
       <c r="Q28" s="16" t="n">
         <f aca="false">P28+R28</f>
-        <v>2.579</v>
+        <v>2.594</v>
       </c>
       <c r="R28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.031</v>
+        <v>0.046</v>
       </c>
       <c r="S28" s="17"/>
       <c r="T28" s="18" t="n">
@@ -15659,11 +15659,11 @@
       </c>
       <c r="E29" s="16" t="n">
         <f aca="false">+D29+F29</f>
-        <v>-3.7539</v>
+        <v>-3.7411</v>
       </c>
       <c r="F29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0039</v>
+        <v>0.0089</v>
       </c>
       <c r="G29" s="16" t="n">
         <f aca="false">W29+0.18</f>
@@ -15671,11 +15671,11 @@
       </c>
       <c r="H29" s="16" t="n">
         <f aca="false">G29+I29</f>
-        <v>2.552</v>
+        <v>2.542</v>
       </c>
       <c r="I29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>-0.005</v>
+        <v>-0.015</v>
       </c>
       <c r="J29" s="16" t="n">
         <f aca="false">X29+0.18</f>
@@ -15683,22 +15683,22 @@
       </c>
       <c r="K29" s="16" t="n">
         <f aca="false">J29+L29</f>
-        <v>2.637</v>
+        <v>2.63</v>
       </c>
       <c r="L29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>-0.007</v>
+        <v>-0.014</v>
       </c>
       <c r="M29" s="16" t="n">
         <v>3.75</v>
       </c>
       <c r="N29" s="16" t="n">
         <f aca="false">+M29+O29</f>
-        <v>3.7505</v>
+        <v>3.7597</v>
       </c>
       <c r="O29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0005</v>
+        <v>0.0097</v>
       </c>
       <c r="P29" s="16" t="n">
         <f aca="false">Y29+0.18</f>
@@ -15706,11 +15706,11 @@
       </c>
       <c r="Q29" s="16" t="n">
         <f aca="false">P29+R29</f>
-        <v>2.582</v>
+        <v>2.592</v>
       </c>
       <c r="R29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.025</v>
+        <v>0.035</v>
       </c>
       <c r="S29" s="17"/>
       <c r="T29" s="18" t="n">
@@ -15746,11 +15746,11 @@
       </c>
       <c r="E30" s="16" t="n">
         <f aca="false">+D30+F30</f>
-        <v>-3.7427</v>
+        <v>-3.7528</v>
       </c>
       <c r="F30" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0073</v>
+        <v>-0.0028</v>
       </c>
       <c r="G30" s="16" t="n">
         <f aca="false">W30+0.18</f>
@@ -15758,11 +15758,11 @@
       </c>
       <c r="H30" s="16" t="n">
         <f aca="false">G30+I30</f>
-        <v>2.625</v>
+        <v>2.611</v>
       </c>
       <c r="I30" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.059</v>
+        <v>0.045</v>
       </c>
       <c r="J30" s="16" t="n">
         <f aca="false">X30+0.18</f>
@@ -15770,22 +15770,22 @@
       </c>
       <c r="K30" s="16" t="n">
         <f aca="false">J30+L30</f>
-        <v>2.668</v>
+        <v>2.709</v>
       </c>
       <c r="L30" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.015</v>
+        <v>0.056</v>
       </c>
       <c r="M30" s="16" t="n">
         <v>3.75</v>
       </c>
       <c r="N30" s="16" t="n">
         <f aca="false">+M30+O30</f>
-        <v>3.7586</v>
+        <v>3.7483</v>
       </c>
       <c r="O30" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0086</v>
+        <v>-0.0017</v>
       </c>
       <c r="P30" s="16" t="n">
         <f aca="false">Y30+0.18</f>
@@ -15793,11 +15793,11 @@
       </c>
       <c r="Q30" s="16" t="n">
         <f aca="false">P30+R30</f>
-        <v>2.621</v>
+        <v>2.56</v>
       </c>
       <c r="R30" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.055</v>
+        <v>-0.006</v>
       </c>
       <c r="S30" s="17"/>
       <c r="T30" s="18" t="n">
@@ -15833,11 +15833,11 @@
       </c>
       <c r="E31" s="16" t="n">
         <f aca="false">+D31+F31</f>
-        <v>-3.7447</v>
+        <v>-3.7471</v>
       </c>
       <c r="F31" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0053</v>
+        <v>0.0029</v>
       </c>
       <c r="G31" s="16" t="n">
         <f aca="false">W31+0.18</f>
@@ -15845,11 +15845,11 @@
       </c>
       <c r="H31" s="16" t="n">
         <f aca="false">G31+I31</f>
-        <v>2.579</v>
+        <v>2.578</v>
       </c>
       <c r="I31" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.013</v>
+        <v>0.012</v>
       </c>
       <c r="J31" s="16" t="n">
         <f aca="false">X31+0.18</f>
@@ -15857,22 +15857,22 @@
       </c>
       <c r="K31" s="16" t="n">
         <f aca="false">J31+L31</f>
-        <v>2.672</v>
+        <v>2.711</v>
       </c>
       <c r="L31" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.019</v>
+        <v>0.058</v>
       </c>
       <c r="M31" s="16" t="n">
         <v>3.75</v>
       </c>
       <c r="N31" s="16" t="n">
         <f aca="false">+M31+O31</f>
-        <v>3.7532</v>
+        <v>3.7476</v>
       </c>
       <c r="O31" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0032</v>
+        <v>-0.0024</v>
       </c>
       <c r="P31" s="16" t="n">
         <f aca="false">Y31+0.18</f>
@@ -15880,11 +15880,11 @@
       </c>
       <c r="Q31" s="16" t="n">
         <f aca="false">P31+R31</f>
-        <v>2.612</v>
+        <v>2.628</v>
       </c>
       <c r="R31" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.046</v>
+        <v>0.062</v>
       </c>
       <c r="S31" s="17"/>
       <c r="T31" s="18"/>
@@ -16098,7 +16098,7 @@
     <row r="2" s="27" customFormat="true" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="str">
         <f>"Kèm theo BBNT số: "&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,7,0)&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,4,0)</f>
-        <v xml:space="preserve">Kèm theo BBNT số: 21.NĐXB6A/CVXD ngày 05 tháng 09 năm 2026</v>
+        <v xml:space="preserve">Kèm theo BBNT số: 21.NĐXB6A/CVXD ngày 08 tháng 09 năm 2026</v>
       </c>
       <c r="B2" s="28"/>
       <c r="C2" s="28"/>
@@ -21292,7 +21292,7 @@
     <row r="2" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="str">
         <f>"Kèm theo BBNT số: "&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,7,0)&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,4,0)</f>
-        <v xml:space="preserve">Kèm theo BBNT số: 24.NĐXB6A/CVXD ngày 06 tháng 09 năm 2026</v>
+        <v xml:space="preserve">Kèm theo BBNT số: 24.NĐXB6A/CVXD ngày 09 tháng 09 năm 2026</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -21578,11 +21578,11 @@
       </c>
       <c r="E23" s="16" t="n">
         <f aca="false">+D23+F23</f>
-        <v>-3.7466</v>
+        <v>-3.7401</v>
       </c>
       <c r="F23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0034</v>
+        <v>0.0099</v>
       </c>
       <c r="G23" s="16" t="n">
         <f aca="false">W23+0.15</f>
@@ -21590,11 +21590,11 @@
       </c>
       <c r="H23" s="16" t="n">
         <f aca="false">G23+I23</f>
-        <v>2.684</v>
+        <v>2.663</v>
       </c>
       <c r="I23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.012</v>
+        <v>-0.009</v>
       </c>
       <c r="J23" s="16" t="n">
         <f aca="false">X23+0.15</f>
@@ -21602,22 +21602,22 @@
       </c>
       <c r="K23" s="16" t="n">
         <f aca="false">J23+L23</f>
-        <v>2.802</v>
+        <v>2.795</v>
       </c>
       <c r="L23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.043</v>
+        <v>0.036</v>
       </c>
       <c r="M23" s="16" t="n">
         <v>3.75</v>
       </c>
       <c r="N23" s="16" t="n">
         <f aca="false">+M23+O23</f>
-        <v>3.7532</v>
+        <v>3.7404</v>
       </c>
       <c r="O23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0032</v>
+        <v>-0.0096</v>
       </c>
       <c r="P23" s="16" t="n">
         <f aca="false">Y23+0.15</f>
@@ -21625,11 +21625,11 @@
       </c>
       <c r="Q23" s="16" t="n">
         <f aca="false">P23+R23</f>
-        <v>2.711</v>
+        <v>2.67</v>
       </c>
       <c r="R23" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.039</v>
+        <v>-0.002</v>
       </c>
       <c r="S23" s="17"/>
       <c r="T23" s="18" t="n">
@@ -21665,11 +21665,11 @@
       </c>
       <c r="E24" s="16" t="n">
         <f aca="false">+D24+F24</f>
-        <v>-3.7538</v>
+        <v>-3.755</v>
       </c>
       <c r="F24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0038</v>
+        <v>-0.005</v>
       </c>
       <c r="G24" s="16" t="n">
         <f aca="false">W24+0.15</f>
@@ -21689,22 +21689,22 @@
       </c>
       <c r="K24" s="16" t="n">
         <f aca="false">J24+L24</f>
-        <v>2.786</v>
+        <v>2.775</v>
       </c>
       <c r="L24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.027</v>
+        <v>0.016</v>
       </c>
       <c r="M24" s="16" t="n">
         <v>3.75</v>
       </c>
       <c r="N24" s="16" t="n">
         <f aca="false">+M24+O24</f>
-        <v>3.7455</v>
+        <v>3.7441</v>
       </c>
       <c r="O24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0045</v>
+        <v>-0.0059</v>
       </c>
       <c r="P24" s="16" t="n">
         <f aca="false">Y24+0.15</f>
@@ -21712,11 +21712,11 @@
       </c>
       <c r="Q24" s="16" t="n">
         <f aca="false">P24+R24</f>
-        <v>2.672</v>
+        <v>2.73</v>
       </c>
       <c r="R24" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0</v>
+        <v>0.058</v>
       </c>
       <c r="S24" s="17"/>
       <c r="T24" s="18" t="n">
@@ -21752,11 +21752,11 @@
       </c>
       <c r="E25" s="16" t="n">
         <f aca="false">+D25+F25</f>
-        <v>-3.7531</v>
+        <v>-3.7481</v>
       </c>
       <c r="F25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0031</v>
+        <v>0.0019</v>
       </c>
       <c r="G25" s="16" t="n">
         <f aca="false">W25+0.15</f>
@@ -21764,11 +21764,11 @@
       </c>
       <c r="H25" s="16" t="n">
         <f aca="false">G25+I25</f>
-        <v>2.725</v>
+        <v>2.701</v>
       </c>
       <c r="I25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.045</v>
+        <v>0.021</v>
       </c>
       <c r="J25" s="16" t="n">
         <f aca="false">X25+0.15</f>
@@ -21787,11 +21787,11 @@
       </c>
       <c r="N25" s="16" t="n">
         <f aca="false">+M25+O25</f>
-        <v>3.7405</v>
+        <v>3.7554</v>
       </c>
       <c r="O25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0095</v>
+        <v>0.0054</v>
       </c>
       <c r="P25" s="16" t="n">
         <f aca="false">Y25+0.15</f>
@@ -21799,11 +21799,11 @@
       </c>
       <c r="Q25" s="16" t="n">
         <f aca="false">P25+R25</f>
-        <v>2.705</v>
+        <v>2.664</v>
       </c>
       <c r="R25" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.025</v>
+        <v>-0.016</v>
       </c>
       <c r="S25" s="17"/>
       <c r="T25" s="18" t="n">
@@ -21839,11 +21839,11 @@
       </c>
       <c r="E26" s="16" t="n">
         <f aca="false">+D26+F26</f>
-        <v>-3.7569</v>
+        <v>-3.7502</v>
       </c>
       <c r="F26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0069</v>
+        <v>-0.0002</v>
       </c>
       <c r="G26" s="16" t="n">
         <f aca="false">W26+0.15</f>
@@ -21851,11 +21851,11 @@
       </c>
       <c r="H26" s="16" t="n">
         <f aca="false">G26+I26</f>
-        <v>2.672</v>
+        <v>2.751</v>
       </c>
       <c r="I26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>-0.015</v>
+        <v>0.064</v>
       </c>
       <c r="J26" s="16" t="n">
         <f aca="false">X26+0.15</f>
@@ -21863,22 +21863,22 @@
       </c>
       <c r="K26" s="16" t="n">
         <f aca="false">J26+L26</f>
-        <v>2.791</v>
+        <v>2.813</v>
       </c>
       <c r="L26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.017</v>
+        <v>0.039</v>
       </c>
       <c r="M26" s="16" t="n">
         <v>3.75</v>
       </c>
       <c r="N26" s="16" t="n">
         <f aca="false">+M26+O26</f>
-        <v>3.7593</v>
+        <v>3.7533</v>
       </c>
       <c r="O26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0093</v>
+        <v>0.0033</v>
       </c>
       <c r="P26" s="16" t="n">
         <f aca="false">Y26+0.15</f>
@@ -21886,11 +21886,11 @@
       </c>
       <c r="Q26" s="16" t="n">
         <f aca="false">P26+R26</f>
-        <v>2.681</v>
+        <v>2.707</v>
       </c>
       <c r="R26" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>-0.006</v>
+        <v>0.02</v>
       </c>
       <c r="S26" s="17"/>
       <c r="T26" s="18" t="n">
@@ -21926,11 +21926,11 @@
       </c>
       <c r="E27" s="16" t="n">
         <f aca="false">+D27+F27</f>
-        <v>-3.7491</v>
+        <v>-3.7429</v>
       </c>
       <c r="F27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0009</v>
+        <v>0.0071</v>
       </c>
       <c r="G27" s="16" t="n">
         <f aca="false">W27+0.15</f>
@@ -21938,11 +21938,11 @@
       </c>
       <c r="H27" s="16" t="n">
         <f aca="false">G27+I27</f>
-        <v>2.686</v>
+        <v>2.69</v>
       </c>
       <c r="I27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>-0.007</v>
+        <v>-0.003</v>
       </c>
       <c r="J27" s="16" t="n">
         <f aca="false">X27+0.15</f>
@@ -21950,22 +21950,22 @@
       </c>
       <c r="K27" s="16" t="n">
         <f aca="false">J27+L27</f>
-        <v>2.804</v>
+        <v>2.838</v>
       </c>
       <c r="L27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.024</v>
+        <v>0.058</v>
       </c>
       <c r="M27" s="16" t="n">
         <v>3.75</v>
       </c>
       <c r="N27" s="16" t="n">
         <f aca="false">+M27+O27</f>
-        <v>3.7587</v>
+        <v>3.7454</v>
       </c>
       <c r="O27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0087</v>
+        <v>-0.0046</v>
       </c>
       <c r="P27" s="16" t="n">
         <f aca="false">Y27+0.15</f>
@@ -21973,11 +21973,11 @@
       </c>
       <c r="Q27" s="16" t="n">
         <f aca="false">P27+R27</f>
-        <v>2.736</v>
+        <v>2.742</v>
       </c>
       <c r="R27" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.043</v>
+        <v>0.049</v>
       </c>
       <c r="S27" s="17"/>
       <c r="T27" s="18" t="n">
@@ -22013,11 +22013,11 @@
       </c>
       <c r="E28" s="16" t="n">
         <f aca="false">+D28+F28</f>
-        <v>-3.7587</v>
+        <v>-3.7475</v>
       </c>
       <c r="F28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0087</v>
+        <v>0.0025</v>
       </c>
       <c r="G28" s="16" t="n">
         <f aca="false">W28+0.15</f>
@@ -22025,11 +22025,11 @@
       </c>
       <c r="H28" s="16" t="n">
         <f aca="false">G28+I28</f>
-        <v>2.712</v>
+        <v>2.768</v>
       </c>
       <c r="I28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.014</v>
+        <v>0.07</v>
       </c>
       <c r="J28" s="16" t="n">
         <f aca="false">X28+0.15</f>
@@ -22037,22 +22037,22 @@
       </c>
       <c r="K28" s="16" t="n">
         <f aca="false">J28+L28</f>
-        <v>2.838</v>
+        <v>2.819</v>
       </c>
       <c r="L28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.053</v>
+        <v>0.034</v>
       </c>
       <c r="M28" s="16" t="n">
         <v>3.75</v>
       </c>
       <c r="N28" s="16" t="n">
         <f aca="false">+M28+O28</f>
-        <v>3.753</v>
+        <v>3.7615</v>
       </c>
       <c r="O28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.003</v>
+        <v>0.0115</v>
       </c>
       <c r="P28" s="16" t="n">
         <f aca="false">Y28+0.15</f>
@@ -22060,11 +22060,11 @@
       </c>
       <c r="Q28" s="16" t="n">
         <f aca="false">P28+R28</f>
-        <v>2.721</v>
+        <v>2.704</v>
       </c>
       <c r="R28" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.023</v>
+        <v>0.006</v>
       </c>
       <c r="S28" s="17"/>
       <c r="T28" s="18" t="n">
@@ -22100,11 +22100,11 @@
       </c>
       <c r="E29" s="16" t="n">
         <f aca="false">+D29+F29</f>
-        <v>-3.7438</v>
+        <v>-3.75</v>
       </c>
       <c r="F29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0062</v>
+        <v>0</v>
       </c>
       <c r="G29" s="16" t="n">
         <f aca="false">W29+0.15</f>
@@ -22112,11 +22112,11 @@
       </c>
       <c r="H29" s="16" t="n">
         <f aca="false">G29+I29</f>
-        <v>2.73</v>
+        <v>2.768</v>
       </c>
       <c r="I29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.023</v>
+        <v>0.061</v>
       </c>
       <c r="J29" s="16" t="n">
         <f aca="false">X29+0.15</f>
@@ -22124,22 +22124,22 @@
       </c>
       <c r="K29" s="16" t="n">
         <f aca="false">J29+L29</f>
-        <v>2.824</v>
+        <v>2.794</v>
       </c>
       <c r="L29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="M29" s="16" t="n">
         <v>3.75</v>
       </c>
       <c r="N29" s="16" t="n">
         <f aca="false">+M29+O29</f>
-        <v>3.7504</v>
+        <v>3.7469</v>
       </c>
       <c r="O29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0004</v>
+        <v>-0.0031</v>
       </c>
       <c r="P29" s="16" t="n">
         <f aca="false">Y29+0.15</f>
@@ -22147,11 +22147,11 @@
       </c>
       <c r="Q29" s="16" t="n">
         <f aca="false">P29+R29</f>
-        <v>2.74</v>
+        <v>2.745</v>
       </c>
       <c r="R29" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.033</v>
+        <v>0.038</v>
       </c>
       <c r="S29" s="17"/>
       <c r="T29" s="18" t="n">
@@ -22187,11 +22187,11 @@
       </c>
       <c r="E30" s="16" t="n">
         <f aca="false">+D30+F30</f>
-        <v>-3.7454</v>
+        <v>-3.7391</v>
       </c>
       <c r="F30" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0046</v>
+        <v>0.0109</v>
       </c>
       <c r="G30" s="16" t="n">
         <f aca="false">W30+0.15</f>
@@ -22199,11 +22199,11 @@
       </c>
       <c r="H30" s="16" t="n">
         <f aca="false">G30+I30</f>
-        <v>2.748</v>
+        <v>2.732</v>
       </c>
       <c r="I30" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.032</v>
+        <v>0.016</v>
       </c>
       <c r="J30" s="16" t="n">
         <f aca="false">X30+0.15</f>
@@ -22211,22 +22211,22 @@
       </c>
       <c r="K30" s="16" t="n">
         <f aca="false">J30+L30</f>
-        <v>2.872</v>
+        <v>2.783</v>
       </c>
       <c r="L30" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.069</v>
+        <v>-0.02</v>
       </c>
       <c r="M30" s="16" t="n">
         <v>3.75</v>
       </c>
       <c r="N30" s="16" t="n">
         <f aca="false">+M30+O30</f>
-        <v>3.7495</v>
+        <v>3.7567</v>
       </c>
       <c r="O30" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>-0.0005</v>
+        <v>0.0067</v>
       </c>
       <c r="P30" s="16" t="n">
         <f aca="false">Y30+0.15</f>
@@ -22234,11 +22234,11 @@
       </c>
       <c r="Q30" s="16" t="n">
         <f aca="false">P30+R30</f>
-        <v>2.727</v>
+        <v>2.697</v>
       </c>
       <c r="R30" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.011</v>
+        <v>-0.019</v>
       </c>
       <c r="S30" s="17"/>
       <c r="T30" s="18" t="n">
@@ -22274,11 +22274,11 @@
       </c>
       <c r="E31" s="16" t="n">
         <f aca="false">+D31+F31</f>
-        <v>-3.7459</v>
+        <v>-3.7592</v>
       </c>
       <c r="F31" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0041</v>
+        <v>-0.0092</v>
       </c>
       <c r="G31" s="16" t="n">
         <f aca="false">W31+0.15</f>
@@ -22286,11 +22286,11 @@
       </c>
       <c r="H31" s="16" t="n">
         <f aca="false">G31+I31</f>
-        <v>2.747</v>
+        <v>2.746</v>
       </c>
       <c r="I31" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.031</v>
+        <v>0.03</v>
       </c>
       <c r="J31" s="16" t="n">
         <f aca="false">X31+0.15</f>
@@ -22298,22 +22298,22 @@
       </c>
       <c r="K31" s="16" t="n">
         <f aca="false">J31+L31</f>
-        <v>2.864</v>
+        <v>2.821</v>
       </c>
       <c r="L31" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.061</v>
+        <v>0.018</v>
       </c>
       <c r="M31" s="16" t="n">
         <v>3.75</v>
       </c>
       <c r="N31" s="16" t="n">
         <f aca="false">+M31+O31</f>
-        <v>3.7534</v>
+        <v>3.7466</v>
       </c>
       <c r="O31" s="16" t="n">
         <f aca="false">RANDBETWEEN(-105,115)/10000</f>
-        <v>0.0034</v>
+        <v>-0.0034</v>
       </c>
       <c r="P31" s="16" t="n">
         <f aca="false">Y31+0.15</f>
@@ -22321,11 +22321,11 @@
       </c>
       <c r="Q31" s="16" t="n">
         <f aca="false">P31+R31</f>
-        <v>2.749</v>
+        <v>2.782</v>
       </c>
       <c r="R31" s="16" t="n">
         <f aca="false">RANDBETWEEN(-20,70)/1000</f>
-        <v>0.033</v>
+        <v>0.066</v>
       </c>
       <c r="S31" s="17"/>
       <c r="T31" s="18"/>
@@ -22539,7 +22539,7 @@
     <row r="2" s="27" customFormat="true" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="str">
         <f>"Kèm theo BBNT số: "&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,7,0)&amp;VLOOKUP(AZ2,'[1]Tuyến XB6A'!$A$2:$G$60,4,0)</f>
-        <v xml:space="preserve">Kèm theo BBNT số: 24.NĐXB6A/CVXD ngày 06 tháng 09 năm 2026</v>
+        <v xml:space="preserve">Kèm theo BBNT số: 24.NĐXB6A/CVXD ngày 09 tháng 09 năm 2026</v>
       </c>
       <c r="B2" s="28"/>
       <c r="C2" s="28"/>
